--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0001T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0001T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.74170535764762</v>
+        <v>7.920527120617738</v>
       </c>
       <c r="D2" t="n">
-        <v>44.7768911093737</v>
+        <v>7.276244805273227</v>
       </c>
       <c r="E2" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F2" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.80291749624018</v>
+        <v>5.81797409313903</v>
       </c>
       <c r="D3" t="n">
-        <v>35.40050521871418</v>
+        <v>5.752582098041055</v>
       </c>
       <c r="E3" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F3" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.67035816057729</v>
+        <v>9.85893320109381</v>
       </c>
       <c r="D4" t="n">
-        <v>51.60126276366534</v>
+        <v>8.385205199095617</v>
       </c>
       <c r="E4" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F4" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.17045762696075</v>
+        <v>6.202699364381123</v>
       </c>
       <c r="D5" t="n">
-        <v>15.42871214911116</v>
+        <v>2.507165724230564</v>
       </c>
       <c r="E5" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F5" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>59.46461766399672</v>
+        <v>9.663000370399468</v>
       </c>
       <c r="D6" t="n">
-        <v>36.0270503326978</v>
+        <v>5.854395679063393</v>
       </c>
       <c r="E6" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F6" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.42054302372905</v>
+        <v>4.45583824135597</v>
       </c>
       <c r="D7" t="n">
-        <v>25.4917005870875</v>
+        <v>4.142401345401719</v>
       </c>
       <c r="E7" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F7" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.58968218580188</v>
+        <v>5.295823355192806</v>
       </c>
       <c r="D8" t="n">
-        <v>33.70214780578502</v>
+        <v>5.476599018440067</v>
       </c>
       <c r="E8" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F8" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.69530475693132</v>
+        <v>3.850487023001339</v>
       </c>
       <c r="D9" t="n">
-        <v>24.75996507284515</v>
+        <v>4.023494324337337</v>
       </c>
       <c r="E9" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F9" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.18661205593517</v>
+        <v>3.930324459089466</v>
       </c>
       <c r="D10" t="n">
-        <v>11.84505093566871</v>
+        <v>1.924820777046165</v>
       </c>
       <c r="E10" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F10" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>48.00370295553618</v>
+        <v>7.800601730274629</v>
       </c>
       <c r="D11" t="n">
-        <v>19.48090961437831</v>
+        <v>3.165647812336475</v>
       </c>
       <c r="E11" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F11" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>41.97823433455896</v>
+        <v>6.821463079365832</v>
       </c>
       <c r="D12" t="n">
-        <v>41.79579345901839</v>
+        <v>6.791816437090489</v>
       </c>
       <c r="E12" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F12" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>15.73146662809149</v>
+        <v>2.556363327064868</v>
       </c>
       <c r="D13" t="n">
-        <v>15.65076388828362</v>
+        <v>2.543249131846089</v>
       </c>
       <c r="E13" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F13" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>38.43326796426003</v>
+        <v>6.245406044192255</v>
       </c>
       <c r="D14" t="n">
-        <v>11.20294481824187</v>
+        <v>1.820478532964304</v>
       </c>
       <c r="E14" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F14" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>39.91525241783205</v>
+        <v>6.486228517897708</v>
       </c>
       <c r="D15" t="n">
-        <v>33.70376402280267</v>
+        <v>5.476861653705433</v>
       </c>
       <c r="E15" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F15" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>34.65053573624959</v>
+        <v>5.630712057140558</v>
       </c>
       <c r="D16" t="n">
-        <v>34.38786622211917</v>
+        <v>5.588028261094365</v>
       </c>
       <c r="E16" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F16" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>17.45700915584154</v>
+        <v>2.83676398782425</v>
       </c>
       <c r="D17" t="n">
-        <v>20.05760592237158</v>
+        <v>3.259360962385382</v>
       </c>
       <c r="E17" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F17" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>22.90675412867714</v>
+        <v>3.722347545910036</v>
       </c>
       <c r="D18" t="n">
-        <v>22.68137856946479</v>
+        <v>3.685724017538029</v>
       </c>
       <c r="E18" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F18" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>27.88910535778474</v>
+        <v>4.53197962064002</v>
       </c>
       <c r="D19" t="n">
-        <v>23.68490523237823</v>
+        <v>3.848797100261463</v>
       </c>
       <c r="E19" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F19" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>53.07381260396732</v>
+        <v>8.624494548144689</v>
       </c>
       <c r="D20" t="n">
-        <v>6.989336796960686</v>
+        <v>1.135767229506111</v>
       </c>
       <c r="E20" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F20" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>18.34511740510793</v>
+        <v>2.981081578330039</v>
       </c>
       <c r="D21" t="n">
-        <v>18.06784003278793</v>
+        <v>2.936024005328039</v>
       </c>
       <c r="E21" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F21" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>49.51225415393916</v>
+        <v>8.045741300015115</v>
       </c>
       <c r="D22" t="n">
-        <v>15.70911541875717</v>
+        <v>2.552731255548041</v>
       </c>
       <c r="E22" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F22" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>9.012619635130003</v>
+        <v>1.464550690708625</v>
       </c>
       <c r="D23" t="n">
-        <v>8.734055594408902</v>
+        <v>1.419284034091447</v>
       </c>
       <c r="E23" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F23" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>36.76951530681521</v>
+        <v>5.975046237357471</v>
       </c>
       <c r="D24" t="n">
-        <v>36.72173707240263</v>
+        <v>5.967282274265427</v>
       </c>
       <c r="E24" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F24" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>14.34381164654872</v>
+        <v>2.330869392564168</v>
       </c>
       <c r="D25" t="n">
-        <v>14.13983723975</v>
+        <v>2.297723551459375</v>
       </c>
       <c r="E25" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F25" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>44.11449750443018</v>
+        <v>7.168605844469904</v>
       </c>
       <c r="D26" t="n">
-        <v>44.44688673477444</v>
+        <v>7.222619094400848</v>
       </c>
       <c r="E26" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F26" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>54.35415919397677</v>
+        <v>8.832550869021226</v>
       </c>
       <c r="D27" t="n">
-        <v>55.92100089064154</v>
+        <v>9.087162644729251</v>
       </c>
       <c r="E27" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F27" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>17.73533924448287</v>
+        <v>2.881992627228467</v>
       </c>
       <c r="D28" t="n">
-        <v>17.90401822227878</v>
+        <v>2.909402961120302</v>
       </c>
       <c r="E28" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F28" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>24.00601453858459</v>
+        <v>3.900977362519996</v>
       </c>
       <c r="D29" t="n">
-        <v>24.26701161162082</v>
+        <v>3.943389386888383</v>
       </c>
       <c r="E29" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F29" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>48.61427844066981</v>
+        <v>7.899820246608845</v>
       </c>
       <c r="D30" t="n">
-        <v>48.53639755008133</v>
+        <v>7.887164601888217</v>
       </c>
       <c r="E30" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F30" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>32.81674645942199</v>
+        <v>5.332721299656074</v>
       </c>
       <c r="D31" t="n">
-        <v>33.059321220468</v>
+        <v>5.37213969832605</v>
       </c>
       <c r="E31" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F31" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>37.66365617696709</v>
+        <v>6.120344128757152</v>
       </c>
       <c r="D32" t="n">
-        <v>37.9294247703197</v>
+        <v>6.163531525176952</v>
       </c>
       <c r="E32" t="n">
-        <v>13.78026367616906</v>
+        <v>2.239292847377472</v>
       </c>
       <c r="F32" t="n">
-        <v>13.13549839620765</v>
+        <v>2.134518489383743</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
